--- a/src/gcdocs/locale/app.xlsx
+++ b/src/gcdocs/locale/app.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Description et catalogue de donnée</t>
+          <t>Description et catalogue de données</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
